--- a/光伏配储项目/电价数据/2026/虎地站.xlsx
+++ b/光伏配储项目/电价数据/2026/虎地站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60377</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80936</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.67961</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5921900000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.59321</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46955</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45595</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51752</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19954</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22072</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21516</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20111</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06221</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15974</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24303</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24111</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22701</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.90738</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22351</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52112</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.53679</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6054400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6057400000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21371</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.78088</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6545700000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93325</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53853</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27476</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39045</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14277</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24343</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34932</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.5126</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75306</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8048</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31248</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12067</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8657100000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79359</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7535599999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51442</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42386</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7004199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74556</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86277</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90361</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48924</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5071600000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46229</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5560499999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.65904</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40691</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50959</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5821499999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85717</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07316</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58374</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93629</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89044</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.56021</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84188</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.25071</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0575</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5027900000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58711</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54644</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53839</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86013</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60521</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7708200000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8391799999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.2119</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15847</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8779600000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26204</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16628</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32508</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10648</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15097</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70978</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04194</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05238</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.96092</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07376</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8783200000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81431</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83456</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48272</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25052</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.54695</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48831</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5773200000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.58443</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66595</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63209</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7017599999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77837</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8660399999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5234099999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77783</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72238</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64481</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6370399999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.58653</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50342</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51142</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5775399999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61153</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58002</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.60146</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23501</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61025</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7365700000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47018</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51074</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57769</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71814</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7174700000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.85939</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45601</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59701</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5497799999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72937</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5627300000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.87227</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.69797</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5785800000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64671</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5137999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43877</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6393300000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5063500000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48873</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.01142</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59245</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6509400000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45587</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4699700000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5339299999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6599299999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5161699999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.71278</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5571799999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43291</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30971</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24469</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14556</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.23853</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25477</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22369</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08588999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14666</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01461</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21143</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09403</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22148</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24184</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20886</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19442</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19735</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03436</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06122</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32322</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30127</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45251</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78495</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87109</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.70723</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.59172</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50222</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.55987</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6513</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8695900000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46092</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.69504</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83401</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50283</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5772699999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49055</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33489</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90455</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40406</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38461</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08569</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65388</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7428400000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22841</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05887</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25503</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48387</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6668099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27315</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22271</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23505</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23066</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23766</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21307</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2048</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20529</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09209999999999999</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22419</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24911</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24866</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22028</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15712</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20224</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22181</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23833</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24161</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22193</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24148</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24152</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22013</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23692</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24031</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24047</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30675</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23659</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.50783</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32604</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22208</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.47018</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.55267</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5323600000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.57053</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48889</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.66484</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.83877</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5766100000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46465</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.54184</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67095</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.53608</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.5592200000000001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43853</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69559</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51425</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.51318</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48885</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49056</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.15103</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24825</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21853</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22457</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33087</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.12479</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63979</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.84126</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.48402</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6301599999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69786</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65538</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7297400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84872</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6874400000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.58738</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.54132</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5347999999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33141</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50378</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.61236</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.61972</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68728</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86956</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.60023</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5206900000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75462</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6067400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6537500000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13967</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.53328</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.13762</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.46163</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46578</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24127</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25298</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26402</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13907</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.12981</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.12885</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23538</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.12309</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25454</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23432</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22452</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22809</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23165</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11874</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11823</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10249</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21181</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09395999999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11384</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18792</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24821</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25025</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25369</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25498</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25435</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.2292</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27066</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15007</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10687</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13522</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10908</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10907</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10731</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10731</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10731</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10747</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22614</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10057</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10048</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11177</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07192</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11506</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14184</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01597</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03843</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26448</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11021</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29948</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5278999999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.20947</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24179</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23373</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11425</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23067</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21614</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11814</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08029</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10767</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08702</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.15219</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10728</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8676799999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85891</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10714</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09906000000000001</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.12913</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.0882</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66028</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59756</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.07572</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97327</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5662699999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7244700000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.61283</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83014</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82836</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83263</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9303400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6088600000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.56284</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33414</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26941</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25864</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23388</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11437</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25713</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25659</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5691799999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49357</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32319</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.71099</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46105</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.54004</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46942</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.73449</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8507</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.13561</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48763</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.56656</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5749299999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.04468</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.88683</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5394600000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64842</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46165</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.46461</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22418</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34107</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50462</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5938600000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.26262</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.03397</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.65398</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8820399999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.65047</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.80683</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74498</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9877899999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89027</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8019500000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72751</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.14606</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.47439</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.49606</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.78837</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.48154</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21648</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.5733200000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.79208</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.49006</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5331399999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67091</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.52203</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6577200000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35145</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.91488</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47569</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5287200000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49443</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.47948</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5077699999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5072300000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.58774</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.48546</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46902</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35204</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04568999999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12087</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22495</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14756</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19213</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15193</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19597</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14078</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.54843</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37923</v>
       </c>
     </row>
   </sheetData>
